--- a/public/templates/forms/A-131-KeyRotationSchedule-FORM.xlsx
+++ b/public/templates/forms/A-131-KeyRotationSchedule-FORM.xlsx
@@ -3,13 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="22340" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="22340" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rotation Schedule" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rotation Log" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Rotation Schedule'!$10:$10</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -17,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -197,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -261,6 +266,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -748,7 +756,6 @@
       <c r="B23" s="24" t="n"/>
       <c r="C23" s="13">
         <f>COUNTA(A11:A20)</f>
-        <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -760,7 +767,6 @@
       <c r="B24" s="24" t="n"/>
       <c r="C24" s="13">
         <f>COUNTIF(F11:F20,"Overdue")</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -772,7 +778,6 @@
       <c r="B25" s="24" t="n"/>
       <c r="C25" s="13">
         <f>COUNTIF(E11:E20,"&lt;"&amp;TODAY())</f>
-        <v/>
       </c>
     </row>
     <row r="26"/>
@@ -790,7 +795,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
+    <row r="29" ht="34.7" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>When a scheduled rotation is missed, the [Owner role] is notified and the rotation is completed within [number] business days; a key suspected of compromise is rotated at once.</t>
@@ -945,7 +950,7 @@
       <c r="F46" s="12" t="n"/>
     </row>
     <row r="47"/>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="82.2" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Drafter's note (internal, delete before publishing): built as one artifact in two sheets, following the Backup Schedule &amp; Media Inventory precedent: the Rotation Schedule sets each key or key-class rotation cadence and next-due date; the Rotation Log records rotations as they are completed. Kept in the Schedule type. Implements the Key &amp; Certificate Management Policy and draws key identifiers from the Key Inventory &amp; Custody Records; point to them and do not restate. No CJIS or Indiana citation: State-maintained IDACS cryptography is out of PSAP scope (add CJIS §5.10.1.2 and 240 IAC 5 only if the agency manages keys that protect CJI). Agency-supplied values in brackets.</t>
@@ -997,7 +1002,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1032,7 +1037,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="34.7" customHeight="1">
       <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Date Rotated</t>
@@ -1165,8 +1170,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1199,7 +1204,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, escalation, sign-off and revision history live on the Schedule tab.</t>
@@ -1340,10 +1345,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
+      <c r="D11" s="26">
+        <v>46266</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
@@ -1414,10 +1417,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
+      <c r="D16" s="26">
+        <v>46086</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
@@ -1560,7 +1561,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="34.7" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
           <t>Small (1–5, no in-house IT)</t>
@@ -1574,7 +1575,7 @@
       <c r="C26" s="23" t="n"/>
       <c r="D26" s="22" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="34.7" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Medium (6–25, shared county IT)</t>
@@ -1588,7 +1589,7 @@
       <c r="C27" s="23" t="n"/>
       <c r="D27" s="22" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="34.7" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
           <t>Large (25+, dedicated IT/security)</t>
@@ -1614,6 +1615,6 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>